--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>92.77637530925638</v>
+        <v>92.77575844130298</v>
       </c>
       <c r="C2">
-        <v>129.2961888546469</v>
+        <v>128.9670902294055</v>
       </c>
       <c r="D2">
-        <v>146.7296141771394</v>
+        <v>146.4440075487502</v>
       </c>
       <c r="E2">
-        <v>156.6071550102643</v>
+        <v>156.5751003882904</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>112.300919584385</v>
+        <v>112.3001941951373</v>
       </c>
       <c r="C3">
-        <v>155.0118333993916</v>
+        <v>154.6727418780609</v>
       </c>
       <c r="D3">
-        <v>173.4922189206746</v>
+        <v>173.1141856161209</v>
       </c>
       <c r="E3">
-        <v>186.1451562353258</v>
+        <v>186.0979100259283</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>99.80053510587648</v>
+        <v>99.79984806906174</v>
       </c>
       <c r="C4">
-        <v>143.1871781758566</v>
+        <v>142.8912673608026</v>
       </c>
       <c r="D4">
-        <v>164.3706505210713</v>
+        <v>164.0504632279912</v>
       </c>
       <c r="E4">
-        <v>177.7673799622309</v>
+        <v>177.7207549847433</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>77.74082220157349</v>
+        <v>77.7403418718624</v>
       </c>
       <c r="C5">
-        <v>105.3708775452284</v>
+        <v>104.9074008041556</v>
       </c>
       <c r="D5">
-        <v>114.5548005703677</v>
+        <v>114.2444646297805</v>
       </c>
       <c r="E5">
-        <v>123.7224839653142</v>
+        <v>123.674608382375</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>68.35171669744066</v>
+        <v>68.35129134572806</v>
       </c>
       <c r="C6">
-        <v>92.41243098372455</v>
+        <v>92.00908994576402</v>
       </c>
       <c r="D6">
-        <v>101.454178557908</v>
+        <v>101.1799834976202</v>
       </c>
       <c r="E6">
-        <v>108.2447638607194</v>
+        <v>108.2029920176508</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7.351923235471475</v>
+        <v>7.351878520200705</v>
       </c>
       <c r="C7">
-        <v>9.818822877887328</v>
+        <v>9.775179972299618</v>
       </c>
       <c r="D7">
-        <v>10.79992752870543</v>
+        <v>10.77047789598165</v>
       </c>
       <c r="E7">
-        <v>11.4633186530728</v>
+        <v>11.45892285346128</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>348.8314742863583</v>
+        <v>348.8290548033453</v>
       </c>
       <c r="C8">
-        <v>490.9312007096121</v>
+        <v>493.8476553098598</v>
       </c>
       <c r="D8">
-        <v>568.6846132057784</v>
+        <v>571.0302748881101</v>
       </c>
       <c r="E8">
-        <v>611.4566408661268</v>
+        <v>611.7815097681862</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>99.8299696618147</v>
+        <v>99.82935374089804</v>
       </c>
       <c r="C9">
-        <v>134.4519058345597</v>
+        <v>133.9569224531737</v>
       </c>
       <c r="D9">
-        <v>147.7654275587027</v>
+        <v>147.3828123584476</v>
       </c>
       <c r="E9">
-        <v>157.8714744315296</v>
+        <v>157.8139959835147</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>43.02656128943718</v>
+        <v>43.02630481577697</v>
       </c>
       <c r="C10">
-        <v>56.40329214572002</v>
+        <v>56.15421184317183</v>
       </c>
       <c r="D10">
-        <v>62.60229058012804</v>
+        <v>62.43691674321689</v>
       </c>
       <c r="E10">
-        <v>65.63186724244187</v>
+        <v>65.6112053572095</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>7.905522639184566</v>
+        <v>7.907966097159567</v>
       </c>
       <c r="C11">
-        <v>9.841183375702865</v>
+        <v>9.799740850775759</v>
       </c>
       <c r="D11">
-        <v>10.8011007964307</v>
+        <v>10.77313934553706</v>
       </c>
       <c r="E11">
-        <v>12.21835427678015</v>
+        <v>12.21473788445947</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>18.90185688857558</v>
+        <v>18.90582923849273</v>
       </c>
       <c r="C12">
-        <v>25.85106063484142</v>
+        <v>25.73528913745696</v>
       </c>
       <c r="D12">
-        <v>28.53290377102535</v>
+        <v>28.4544150378914</v>
       </c>
       <c r="E12">
-        <v>29.52094279478744</v>
+        <v>29.5096737334689</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>24.1823231006262</v>
+        <v>24.18217886103426</v>
       </c>
       <c r="C13">
-        <v>31.42402546282844</v>
+        <v>31.2834102150737</v>
       </c>
       <c r="D13">
-        <v>35.21227381206855</v>
+        <v>35.118859210552</v>
       </c>
       <c r="E13">
-        <v>37.35046270140714</v>
+        <v>37.33858862071246</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>92.77575844130298</v>
+        <v>3.551225203494851</v>
       </c>
       <c r="C2">
-        <v>128.9670902294055</v>
+        <v>10.4901460952148</v>
       </c>
       <c r="D2">
-        <v>146.4440075487502</v>
+        <v>23.12273803401319</v>
       </c>
       <c r="E2">
-        <v>156.5751003882904</v>
+        <v>37.63824528564674</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>112.3001941951373</v>
+        <v>37.5861874449031</v>
       </c>
       <c r="C3">
-        <v>154.6727418780609</v>
+        <v>95.57014945311084</v>
       </c>
       <c r="D3">
-        <v>173.1141856161209</v>
+        <v>130.0122863402704</v>
       </c>
       <c r="E3">
-        <v>186.0979100259283</v>
+        <v>155.0815916882736</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>99.79984806906174</v>
+        <v>3.789867648192218</v>
       </c>
       <c r="C4">
-        <v>142.8912673608026</v>
+        <v>10.20651909720019</v>
       </c>
       <c r="D4">
-        <v>164.0504632279912</v>
+        <v>18.68929327913824</v>
       </c>
       <c r="E4">
-        <v>177.7207549847433</v>
+        <v>26.13540514481519</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>77.7403418718624</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>104.9074008041556</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>114.2444646297805</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>123.674608382375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>68.35129134572806</v>
+        <v>22.94309080136327</v>
       </c>
       <c r="C6">
-        <v>92.00908994576402</v>
+        <v>39.24863277406717</v>
       </c>
       <c r="D6">
-        <v>101.1799834976202</v>
+        <v>39.62293060046666</v>
       </c>
       <c r="E6">
-        <v>108.2029920176508</v>
+        <v>35.0516734705066</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7.351878520200705</v>
+        <v>2.450626173400235</v>
       </c>
       <c r="C7">
-        <v>9.775179972299618</v>
+        <v>6.516786648199745</v>
       </c>
       <c r="D7">
-        <v>10.77047789598165</v>
+        <v>7.898350457053212</v>
       </c>
       <c r="E7">
-        <v>11.45892285346128</v>
+        <v>9.167138282769026</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>348.8290548033453</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>493.8476553098598</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>571.0302748881101</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>611.7815097681862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>99.82935374089804</v>
+        <v>179.3051499229722</v>
       </c>
       <c r="C9">
-        <v>133.9569224531737</v>
+        <v>383.7509904093332</v>
       </c>
       <c r="D9">
-        <v>147.3828123584476</v>
+        <v>573.7913374343444</v>
       </c>
       <c r="E9">
-        <v>157.8139959835147</v>
+        <v>754.7625894863745</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>43.02630481577697</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>56.15421184317183</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>62.43691674321689</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>65.6112053572095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>7.907966097159567</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>9.799740850775759</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>10.77313934553706</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>12.21473788445947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>18.90582923849273</v>
+        <v>232.2023642368723</v>
       </c>
       <c r="C12">
-        <v>25.73528913745696</v>
+        <v>343.5661099850504</v>
       </c>
       <c r="D12">
-        <v>28.4544150378914</v>
+        <v>321.5348899281728</v>
       </c>
       <c r="E12">
-        <v>29.5096737334689</v>
+        <v>257.2638222917802</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>24.18217886103426</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>31.2834102150737</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>35.118859210552</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>37.33858862071246</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.551225203494851</v>
+        <v>11.99973881636015</v>
       </c>
       <c r="C2">
-        <v>10.4901460952148</v>
+        <v>16.68077334703688</v>
       </c>
       <c r="D2">
-        <v>23.12273803401319</v>
+        <v>18.94126085660481</v>
       </c>
       <c r="E2">
-        <v>37.63824528564674</v>
+        <v>20.2516297508208</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>37.5861874449031</v>
+        <v>71.24543888347308</v>
       </c>
       <c r="C3">
-        <v>95.57014945311084</v>
+        <v>98.12741159881054</v>
       </c>
       <c r="D3">
-        <v>130.0122863402704</v>
+        <v>109.8270240721419</v>
       </c>
       <c r="E3">
-        <v>155.0815916882736</v>
+        <v>118.0641526946571</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.789867648192218</v>
+        <v>9.244617505344666</v>
       </c>
       <c r="C4">
-        <v>10.20651909720019</v>
+        <v>13.23624371342172</v>
       </c>
       <c r="D4">
-        <v>18.68929327913824</v>
+        <v>15.19625343585603</v>
       </c>
       <c r="E4">
-        <v>26.13540514481519</v>
+        <v>16.46255414595518</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22.94309080136327</v>
+        <v>25.25765757258952</v>
       </c>
       <c r="C6">
-        <v>39.24863277406717</v>
+        <v>33.99985635473942</v>
       </c>
       <c r="D6">
-        <v>39.62293060046666</v>
+        <v>37.38875046934827</v>
       </c>
       <c r="E6">
-        <v>35.0516734705066</v>
+        <v>39.98394275958725</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.450626173400235</v>
+        <v>4.656189729460445</v>
       </c>
       <c r="C7">
-        <v>6.516786648199745</v>
+        <v>6.190947315789757</v>
       </c>
       <c r="D7">
-        <v>7.898350457053212</v>
+        <v>6.821302667455048</v>
       </c>
       <c r="E7">
-        <v>9.167138282769026</v>
+        <v>7.257317807192146</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>179.3051499229722</v>
+        <v>332.9659437726078</v>
       </c>
       <c r="C9">
-        <v>383.7509904093332</v>
+        <v>446.7933672620987</v>
       </c>
       <c r="D9">
-        <v>573.7913374343444</v>
+        <v>491.5734237863475</v>
       </c>
       <c r="E9">
-        <v>754.7625894863745</v>
+        <v>526.3650834559118</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>232.2023642368723</v>
+        <v>215.9811504777177</v>
       </c>
       <c r="C12">
-        <v>343.5661099850504</v>
+        <v>294.0012461589228</v>
       </c>
       <c r="D12">
-        <v>321.5348899281728</v>
+        <v>325.0646781227466</v>
       </c>
       <c r="E12">
-        <v>257.2638222917802</v>
+        <v>337.1200068918442</v>
       </c>
     </row>
     <row r="13" spans="1:5">
